--- a/App/TestCases_App/User_maitre.xlsx
+++ b/App/TestCases_App/User_maitre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\App\TestCases_App\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46549B97-E263-4BA1-98F6-E309E755B563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE3D3F1-A7AB-4D17-93AE-2B2A5B7B925F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -205,9 +205,6 @@
     <t>1. The maitre page is correctly.</t>
   </si>
   <si>
-    <t>La barra superior no entra entera: maitre001.jpg</t>
-  </si>
-  <si>
     <t>El menu sale cortado: Waiter002.jpg</t>
   </si>
   <si>
@@ -233,6 +230,10 @@
   </si>
   <si>
     <t>USERMAI012</t>
+  </si>
+  <si>
+    <t>La barra superior no entra entera: maitre001.jpg
+Alerta erronea: alerta.jpg</t>
   </si>
 </sst>
 </file>
@@ -338,38 +339,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6565"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -761,7 +731,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -772,19 +742,19 @@
         <v>41</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>61</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>62</v>
       </c>
       <c r="H3" s="7"/>
     </row>
@@ -805,7 +775,7 @@
         <v>8</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -827,7 +797,7 @@
         <v>8</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1003,13 +973,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>58</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -1020,32 +990,18 @@
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="G2 G4:G13">
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="PTE">
+  <conditionalFormatting sqref="G2:G13">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="BL">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="7" operator="containsText" text="KO">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
-      <formula>NOT(ISERROR(SEARCH("PTE",G3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
-      <formula>NOT(ISERROR(SEARCH("BL",G3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
-      <formula>NOT(ISERROR(SEARCH("KO",G3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",G3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
